--- a/AAII_Financials/Quarterly/CBRL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CBRL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
   <si>
     <t>CBRL</t>
   </si>
@@ -656,544 +656,557 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46143</v>
+      </c>
+      <c r="E7" s="2">
         <v>46052</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45961</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45870</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45779</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45688</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45597</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45506</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45408</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45317</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45226</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45135</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45044</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44953</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44862</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44771</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44680</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44589</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44498</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44407</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44316</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44225</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44134</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44043</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43952</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43861</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43770</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43679</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43588</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43497</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43406</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43315</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43217</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43126</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43035</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42944</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42853</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42762</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42671</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42580</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>797400</v>
+      </c>
+      <c r="E8" s="3">
         <v>874800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>797200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>868000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>821100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>949400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>845100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>894400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>817100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>935400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>823800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>836700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>832700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>933900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>839500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>830400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>790200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>862300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>784900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>784400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>713400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>677200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>646500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>495100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>432500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>846100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>749000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>787100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>739600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>811700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>733500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>810900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>721400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>787800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>710400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>743200</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>700400</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>772700</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>710000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>745600</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>543100</v>
+      </c>
+      <c r="E9" s="3">
         <v>608400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>549700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>581300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>552100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>636200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>566100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>607300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>553900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>638000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>560000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>562400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>560100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>326600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>281500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>273400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>250000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>283600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>242800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>235800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>205400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>225100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>199000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>150800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>137100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>272200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>219800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>226500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>217100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>265200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>222300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>246000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>217700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>261000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>210700</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>217400</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>205900</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>254900</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>213100</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>227900</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>254300</v>
+      </c>
+      <c r="E10" s="3">
         <v>266400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>247500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>286700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>269100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>313300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>279000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>287100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>263300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>297400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>263800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>274300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>272600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>607300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>558000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>557000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>540200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>578700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>542100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>548600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>508000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>452100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>447500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>344300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>295400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>573900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>529200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>560600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>522500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>546500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>511200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>564900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>503700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>526800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>499700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>525800</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>494500</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>517800</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>496900</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>517700</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1236,8 +1249,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1358,8 +1372,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1480,55 +1497,58 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-47400</v>
+      </c>
+      <c r="E14" s="3">
         <v>400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>13000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>700</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>27600</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
         <v>100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>13900</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1549,23 +1569,23 @@
         <v>0</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>-217700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-65800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>18300</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3">
         <v>1300</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1581,8 +1601,8 @@
       <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK14" s="3">
         <v>0</v>
@@ -1602,50 +1622,53 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E15" s="3">
         <v>30500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>30200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>31900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>31000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>30200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>29200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>29000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>28300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>27800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>26700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>27700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>26400</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1724,8 +1747,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1765,252 +1791,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>790600</v>
+      </c>
+      <c r="E17" s="3">
         <v>873900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>826500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>847800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>805600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>917900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>837300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>872200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>808800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>904600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>812400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>795400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>802000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>894900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>815900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>797400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>759700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>815600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>742000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>721700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>660900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>662800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>409300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>455000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>511500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>767000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>685700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>707700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>674500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>735000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>671900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>728100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>658100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>711100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>639500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>660000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>628900</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>690000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>634200</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>668000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E18" s="3">
         <v>900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-29300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>20200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>15600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>31600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>7800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>22200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>8400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>30800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>11400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>41300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>30700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>39000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>23600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>33000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>30500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>46700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>42900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>62700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>52500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>14400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>237200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>40100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-79000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>79100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>63300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>79400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>65100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>76700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>61600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>82800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>63300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>76700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>70900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>83200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>71500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>82700</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>75800</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>77600</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2053,8 +2086,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2094,8 +2128,8 @@
       <c r="O20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
+      <c r="P20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -2128,17 +2162,17 @@
         <v>0</v>
       </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-132800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-5900</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
         <v>0</v>
       </c>
@@ -2175,496 +2209,511 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>37800</v>
+      </c>
+      <c r="E21" s="3">
         <v>31400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>52000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>46600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>61800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>36900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>51200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>36700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>58500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>38100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>69000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>57100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>64500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>48400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>59300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>56400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>72200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>68700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>90300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>79700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>41800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>263500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>70000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-181800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>105200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>86100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>108400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>92500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>102900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>86500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>108200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>87300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>99400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>92500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>105900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>93300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>104000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>96300</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>98400</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E22" s="3">
         <v>4000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4700</v>
-      </c>
-      <c r="G22" s="3">
-        <v>5000</v>
       </c>
       <c r="H22" s="3">
         <v>5000</v>
       </c>
       <c r="I22" s="3">
+        <v>5000</v>
+      </c>
+      <c r="J22" s="3">
         <v>5800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>5100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>4900</v>
-      </c>
-      <c r="N22" s="3">
-        <v>4500</v>
       </c>
       <c r="O22" s="3">
         <v>4500</v>
       </c>
       <c r="P22" s="3">
+        <v>4500</v>
+      </c>
+      <c r="Q22" s="3">
         <v>4400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>3500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>2600</v>
-      </c>
-      <c r="S22" s="3">
-        <v>2200</v>
       </c>
       <c r="T22" s="3">
         <v>2200</v>
       </c>
       <c r="U22" s="3">
+        <v>2200</v>
+      </c>
+      <c r="V22" s="3">
         <v>2600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>25000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>9600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>10800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>10700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>9900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>5300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>3500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>3600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>3900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>4100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>4200</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>4300</v>
       </c>
       <c r="AH22" s="3">
         <v>4300</v>
       </c>
       <c r="AI22" s="3">
+        <v>4300</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>3600</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>3700</v>
-      </c>
-      <c r="AK22" s="3">
-        <v>3600</v>
       </c>
       <c r="AL22" s="3">
         <v>3600</v>
       </c>
       <c r="AM22" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AN22" s="3">
         <v>3400</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>3600</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>3700</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>50500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-36500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>9900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>24100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>16500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-24500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>25700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>36700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>12300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>34600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>20100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>30400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>28300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>44500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>40300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>37700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>42900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>226400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>30100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-217200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>72000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>53800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>75500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>61000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>72500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>57300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>78500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>59700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>73000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>67200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>79700</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>68100</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>79100</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>72100</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>74100</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E24" s="3">
         <v>-4900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-11900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-4300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-2700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-3600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-15300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-3000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>6800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>6900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>9400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-10400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>55700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>5100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-55200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>10900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>10600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>10500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>10600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>11800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>10100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>18100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>11000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>11400</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>20800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>25800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>21200</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>26300</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>23700</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>23100</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2785,252 +2834,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>42800</v>
+      </c>
+      <c r="E26" s="3">
         <v>1300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-24600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>12600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>22200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>18100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>26500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>37500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>14000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>30500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>17100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>33400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>27500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>37600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>33400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>36400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>33500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>14000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>170700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>25100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-161900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>61200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>43200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>65000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>50400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>60800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>47200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>60400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>48700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>61600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>46400</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>53900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>46900</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>52700</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>48400</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>51000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>42800</v>
+      </c>
+      <c r="E27" s="3">
         <v>1300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-24600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>12600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>22200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>18100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>26500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>37500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>14000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>30500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>17100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>33400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>27500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>37600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>33400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>36400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>33500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>14000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>170700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>25100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-161900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>61200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>43200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>65000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>50400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>60800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>47200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>60400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>48700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>61600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>46400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>53900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>46900</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>52700</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>48400</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>51000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3151,8 +3209,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3228,17 +3289,17 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -3246,18 +3307,18 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI29" s="3">
         <v>1000</v>
       </c>
-      <c r="AI29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3">
         <v>29500</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3273,8 +3334,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3395,8 +3459,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3517,8 +3584,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3558,8 +3628,8 @@
       <c r="O32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
+      <c r="P32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -3592,17 +3662,17 @@
         <v>0</v>
       </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>132800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>3500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>5900</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
         <v>0</v>
       </c>
@@ -3639,130 +3709,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>42800</v>
+      </c>
+      <c r="E33" s="3">
         <v>1300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-24600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>12600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>22200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>18100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>26500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>37500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>14000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>30500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>17100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>33400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>27500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>37600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>33400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>36400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>33500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>14000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>170700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>25100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-161900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>61200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>43200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>65000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>50400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>60800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>47200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>61400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>48700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>91100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>46400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>53900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>46900</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>52700</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>48400</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>51000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3883,257 +3959,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>42800</v>
+      </c>
+      <c r="E35" s="3">
         <v>1300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-24600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>12600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>22200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>18100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>26500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>37500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>14000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>30500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>17100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>33400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>27500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>37600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>33400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>36400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>33500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>14000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>170700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>25100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-161900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>61200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>43200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>65000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>50400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>60800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>47200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>61400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>48700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>91100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>46400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>53900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>46900</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>52700</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>48400</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>51000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46143</v>
+      </c>
+      <c r="E38" s="2">
         <v>46052</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45961</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45870</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45779</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45688</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45597</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45506</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45408</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45317</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45226</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45135</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45044</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44953</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44862</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44771</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44680</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44589</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44498</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44407</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44316</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44225</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44134</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44043</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43952</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43861</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43770</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43679</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43588</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43497</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43406</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43315</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43217</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43126</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43035</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42944</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42853</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42762</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42671</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42580</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4176,8 +4261,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4220,130 +4306,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E41" s="3">
         <v>8600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>39600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>10300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>12000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>12600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>13900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>25100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>22500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>49400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>38700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>45100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>24800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>79700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>125900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>144600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>384600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>568800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>597600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>437000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>363300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>72800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>43200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>36900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>167600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>169600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>101600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>114700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>174300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>168800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>120200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>161000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>183700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>185700</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>125100</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>151000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4464,252 +4554,261 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E43" s="3">
         <v>49600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>39700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>47900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>53100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>51000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>39900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>49100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>56500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>41500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>32200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>32500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>32100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>36500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>32900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>34700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>52000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>44600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>44900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>48500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>54600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>70500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>48900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>49000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>20600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>26700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>33500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>32200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>22200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>17000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>21500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>19500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>21300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>24000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>18100</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>22400</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>19900</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>19700</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>18900</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>35600</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>179900</v>
+      </c>
+      <c r="E44" s="3">
         <v>180300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>209100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>180600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>168700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>173000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>201900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>181000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>175300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>172700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>207300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>189400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>184800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>187300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>231000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>213200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>192400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>153900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>159600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>138300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>132400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>134800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>155700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>139100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>146300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>157400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>188700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>155000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>152600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>151400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>181600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>156300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>157000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>159600</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>191500</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>156400</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>155500</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>155900</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>187200</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>152300</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4749,211 +4848,217 @@
       <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3">
         <v>35500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>28600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>24200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>24900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>28400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>26800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>22200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>22300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>22700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>22600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>17900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>27200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>29200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>28000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>18300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>18800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>21200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>21000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>16300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>17400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>20600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>19500</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>19100</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>19000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>21000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>20300</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>16900</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>290600</v>
+      </c>
+      <c r="E46" s="3">
         <v>283700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>305600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>313100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>276800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>280300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>310400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>278200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>279000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>267800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>287700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>282300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>273000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>308700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>331200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>317300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>294100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>306600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>357200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>353600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>593900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>796800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>824900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>643000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>557400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>286100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>293400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>242400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>361200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>359100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>325700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>306800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>370100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>373000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>349200</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>358900</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>378100</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>382200</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>351500</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>355700</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4993,8 +5098,8 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -5030,17 +5135,17 @@
         <v>0</v>
       </c>
       <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3">
         <v>79500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>83100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>89100</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF47" s="3" t="s">
         <v>8</v>
       </c>
@@ -5053,8 +5158,8 @@
       <c r="AI47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ47" s="3">
-        <v>0</v>
+      <c r="AJ47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK47" s="3">
         <v>0</v>
@@ -5074,130 +5179,136 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1720400</v>
+      </c>
+      <c r="E48" s="3">
         <v>1742400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1768100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1773100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1793300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1798900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1812700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1810700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1805700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1843200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1859800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1861300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1867000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1875700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1884500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1903100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1905700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1913600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1934000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1954300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1967500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1993600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2015900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1822000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1606800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1642400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1651500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1169000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1166400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1162200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1158000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1149100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1126800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1114200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1105800</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1098100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1093400</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>1088600</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>1084700</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>1080200</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5208,7 +5319,7 @@
         <v>24300</v>
       </c>
       <c r="F49" s="3">
-        <v>24400</v>
+        <v>24300</v>
       </c>
       <c r="G49" s="3">
         <v>24400</v>
@@ -5223,22 +5334,22 @@
         <v>24400</v>
       </c>
       <c r="K49" s="3">
+        <v>24400</v>
+      </c>
+      <c r="L49" s="3">
         <v>24500</v>
-      </c>
-      <c r="L49" s="3">
-        <v>29200</v>
       </c>
       <c r="M49" s="3">
         <v>29200</v>
       </c>
       <c r="N49" s="3">
+        <v>29200</v>
+      </c>
+      <c r="O49" s="3">
         <v>28100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>26800</v>
-      </c>
-      <c r="P49" s="3">
-        <v>25900</v>
       </c>
       <c r="Q49" s="3">
         <v>25900</v>
@@ -5253,25 +5364,25 @@
         <v>25900</v>
       </c>
       <c r="U49" s="3">
-        <v>26000</v>
+        <v>25900</v>
       </c>
       <c r="V49" s="3">
         <v>26000</v>
       </c>
       <c r="W49" s="3">
+        <v>26000</v>
+      </c>
+      <c r="X49" s="3">
         <v>26100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>25800</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>25700</v>
       </c>
       <c r="Z49" s="3">
         <v>25700</v>
       </c>
       <c r="AA49" s="3">
-        <v>6400</v>
+        <v>25700</v>
       </c>
       <c r="AB49" s="3">
         <v>6400</v>
@@ -5279,8 +5390,8 @@
       <c r="AC49" s="3">
         <v>6400</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>8</v>
+      <c r="AD49" s="3">
+        <v>6400</v>
       </c>
       <c r="AE49" s="3" t="s">
         <v>8</v>
@@ -5297,8 +5408,8 @@
       <c r="AI49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ49" s="3">
-        <v>0</v>
+      <c r="AJ49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK49" s="3">
         <v>0</v>
@@ -5318,8 +5429,11 @@
       <c r="AP49" s="3">
         <v>0</v>
       </c>
+      <c r="AQ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5440,8 +5554,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5562,130 +5679,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>52600</v>
+      </c>
+      <c r="E52" s="3">
         <v>53300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>53400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>51400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>44600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>46000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>45500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>48200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>47900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>44800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>42900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>46400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>46700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>46400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>45400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>48600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>53400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>56200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>55600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>57800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>55500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>55900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>53700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>53600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>65300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>122500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>103500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>80800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>67500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>66500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>75900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>71500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>71400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>69700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>66900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>65000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>63500</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>64100</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>62900</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>61700</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5806,130 +5929,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2087900</v>
+      </c>
+      <c r="E54" s="3">
         <v>2103800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2151400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2161900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2139000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2149600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2193000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2161500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2157100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2185100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2219600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2218100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2213500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2256700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2287100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2294900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2279100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2302400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2372700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2391700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2642900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2872000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2920100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2544300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2235900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2136900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2137900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1581200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1595100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1587800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1559600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1527400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1568300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1556900</v>
-      </c>
-      <c r="AK54" s="3">
-        <v>1521900</v>
       </c>
       <c r="AL54" s="3">
         <v>1521900</v>
       </c>
       <c r="AM54" s="3">
+        <v>1521900</v>
+      </c>
+      <c r="AN54" s="3">
         <v>1535000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>1534900</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>1499100</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>1497700</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5972,8 +6101,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6016,204 +6146,208 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>131000</v>
+      </c>
+      <c r="E57" s="3">
         <v>126300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>157400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>169800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>121100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>143200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>159600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>162300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>137700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>136400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>143300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>165500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>132000</v>
-      </c>
-      <c r="P57" s="3">
-        <v>135500</v>
       </c>
       <c r="Q57" s="3">
         <v>135500</v>
       </c>
       <c r="R57" s="3">
+        <v>135500</v>
+      </c>
+      <c r="S57" s="3">
         <v>169900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>125400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>123900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>138200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>135200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>113700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>118300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>136100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>103500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>88100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>123300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>145900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>132200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>115300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>117900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>131200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>122300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>104700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>106500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>130100</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>118400</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>98500</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>100400</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>119000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>132500</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>203300</v>
+      </c>
+      <c r="E58" s="3">
         <v>206000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>208100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>200100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>53800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>55500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>57400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>49900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>51800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>54500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>57500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>46400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>47900</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R58" s="3">
+      <c r="R58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S58" s="3">
         <v>100</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V58" s="3">
+      <c r="V58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W58" s="3">
         <v>100</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y58" s="3">
-        <v>39400</v>
+      <c r="Y58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z58" s="3">
         <v>39400</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>8</v>
+      <c r="AA58" s="3">
+        <v>39400</v>
       </c>
       <c r="AB58" s="3" t="s">
         <v>8</v>
@@ -6230,8 +6364,8 @@
       <c r="AF58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG58" s="3">
-        <v>0</v>
+      <c r="AG58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH58" s="3">
         <v>0</v>
@@ -6260,335 +6394,344 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>245700</v>
+      </c>
+      <c r="E59" s="3">
         <v>200400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>187100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>159800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>248100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>255600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>186700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>153100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>256700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>268000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>261100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>187800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>269300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>335300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>334000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>332300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>340200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>354900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>311400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>330000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>335300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>320400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>269200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>308200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>265400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>321600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>296700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>260300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>248400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>262200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>245100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>242300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>246900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>258600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>245700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>257400</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>239800</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>259200</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>234500</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>236300</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>580100</v>
+      </c>
+      <c r="E60" s="3">
         <v>581000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>593900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>625600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>423000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>454200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>448100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>454200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>446200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>458800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>461900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>489000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>449200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>470800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>469500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>502300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>465600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>478900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>449600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>465300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>449000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>438700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>444600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>451100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>353400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>444900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>442700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>392500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>363800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>380100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>376300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>364600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>351600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>365100</v>
-      </c>
-      <c r="AK60" s="3">
-        <v>375800</v>
       </c>
       <c r="AL60" s="3">
         <v>375800</v>
       </c>
       <c r="AM60" s="3">
+        <v>375800</v>
+      </c>
+      <c r="AN60" s="3">
         <v>338300</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>359600</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>353500</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>368800</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>944800</v>
+      </c>
+      <c r="E61" s="3">
         <v>1000400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1033200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>979500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1142500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1127100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1194200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1152600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1153500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1141800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1172200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1117300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1155700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>454100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>483700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>423200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>372900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>327400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>377000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>327300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>575300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>835000</v>
-      </c>
-      <c r="Y61" s="3">
-        <v>910000</v>
       </c>
       <c r="Z61" s="3">
         <v>910000</v>
       </c>
       <c r="AA61" s="3">
+        <v>910000</v>
+      </c>
+      <c r="AB61" s="3">
         <v>940000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>460000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>485000</v>
-      </c>
-      <c r="AD61" s="3">
-        <v>400000</v>
       </c>
       <c r="AE61" s="3">
         <v>400000</v>
@@ -6626,130 +6769,136 @@
       <c r="AP61" s="3">
         <v>400000</v>
       </c>
+      <c r="AQ61" s="3">
+        <v>400000</v>
+      </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>97500</v>
+      </c>
+      <c r="E62" s="3">
         <v>96500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>95500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>23800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>104200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>107300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>110000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>46900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>130800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>122500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>125300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>53700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>134600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>845300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>846300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>857900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>876400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>892100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>916900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>935500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>970500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>989700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>973900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>764800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>550200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>602100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>604400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>184000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>183300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>179100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>183100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>181000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>176400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>176200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>198400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>201600</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>194800</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>193500</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>198500</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>202400</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6870,8 +7019,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6992,8 +7144,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7114,130 +7269,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1622400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1678000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1722600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1700200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1669700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1688600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1752300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1721300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1730500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1723100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1759400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1734300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1739600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1770200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1799500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1783400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1714900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1698300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1743500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1728100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1994800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2263400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2328500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2125900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1843700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1507000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1532100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>976500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>947000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>959200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>959400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>945600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>928000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>941300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>974200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>977400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>933100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>953200</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>952000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>971200</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7280,8 +7441,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7402,8 +7564,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7524,8 +7689,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7646,8 +7814,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7768,130 +7939,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>453500</v>
+      </c>
+      <c r="E72" s="3">
         <v>416400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>420900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>451000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>449900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>443000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>426500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>427400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>414900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>453200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>456000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>479700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>471200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>486300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>487300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>511300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>564000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>603900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>629000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>663400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>656500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>623100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>609100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>438500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>411400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>607400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>577500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>561700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>600600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>580300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>549800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>532800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>592100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>572300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>510300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>492800</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>552800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>533800</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>509000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>488500</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8012,8 +8189,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8134,8 +8314,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8256,130 +8439,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>465500</v>
+      </c>
+      <c r="E76" s="3">
         <v>425800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>428800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>461700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>469300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>460900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>440700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>440100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>426600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>462000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>460300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>483800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>473900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>486500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>487500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>511500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>564200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>604100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>629200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>663600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>648100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>608600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>591600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>418400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>392200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>629900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>605800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>604700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>648000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>628600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>600200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>581800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>640400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>615600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>547700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>544500</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>602000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>581700</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>547100</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>526400</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8500,257 +8689,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46143</v>
+      </c>
+      <c r="E80" s="2">
         <v>46052</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45961</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45870</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45779</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45688</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45597</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45506</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45408</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45317</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45226</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45135</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45044</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44953</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44862</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44771</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44680</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44589</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44498</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44407</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44316</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44225</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44134</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44043</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43952</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43861</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43770</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43679</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43588</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43497</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43406</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43315</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43217</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43126</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43035</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42944</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42853</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42762</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42671</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42580</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>42800</v>
+      </c>
+      <c r="E81" s="3">
         <v>1300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-24600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>12600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>22200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>18100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>26500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>37500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>14000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>30500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>17100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>33400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>27500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>37600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>33400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>36400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>33500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>14000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>170700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>25100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-161900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>61200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>43200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>65000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>50400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>60800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>47200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>61400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>48700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>91100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>46400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>53900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>46900</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>52700</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>48400</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>51000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8793,130 +8991,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E83" s="3">
         <v>30200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>29200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>29000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>28300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>27800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>26700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>27700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>26400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>25600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>24800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>26300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>25900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>25600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>24800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>26300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>25900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>25600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>25800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>27700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>27200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>27400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>26400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>29900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>30000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>29600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>28700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>29000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>27400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>26200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>24800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>25400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>24000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>22700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>21600</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>22700</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>21800</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>21300</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>20500</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>20700</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9037,8 +9239,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9159,8 +9364,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9281,8 +9489,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9403,8 +9614,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9525,130 +9739,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>94700</v>
+      </c>
+      <c r="E89" s="3">
         <v>51300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-53400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>102200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>23000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>98100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>69500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>37600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>77700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-15800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>99200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>50400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>101400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>98900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>84800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>23000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>89400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>91200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>64300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>57000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>73800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-96800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>139200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>44800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>110200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>61700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>131200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>59600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>109600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>72500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>110200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>38300</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>117700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>53600</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>114600</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>34900</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>122000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9691,130 +9911,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-26800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-35500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-45500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-36600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-38100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-39000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-47500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-29400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-26700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-24700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-39400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-38700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-27100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-21800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-38400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-29500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-16300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-14100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-26300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-15700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-18000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-11400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-213700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-25300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-30500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-27900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-34400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-33600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-33200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-37100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-50300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-38300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-33100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-30600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-29300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-28100</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-26800</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-26400</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-44000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9935,8 +10159,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10057,130 +10284,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-26100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-26400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-34100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-45300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-35300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-37300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-38800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-44400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-29000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-26400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-24600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-37700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-38500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-26700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-21500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-38200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-29000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-15700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-15500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-26000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-14900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-18000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>137100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-7900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-26600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-47400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-75300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-138400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-33400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-33100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-36700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-49900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-38200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-32700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-30400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-29200</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-27900</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-26500</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-26100</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-43700</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10223,130 +10456,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E96" s="3">
         <v>5700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>6300</v>
-      </c>
-      <c r="F96" s="3">
-        <v>5600</v>
       </c>
       <c r="G96" s="3">
         <v>5600</v>
       </c>
       <c r="H96" s="3">
+        <v>5600</v>
+      </c>
+      <c r="I96" s="3">
         <v>5800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>6100</v>
-      </c>
-      <c r="J96" s="3">
-        <v>28900</v>
       </c>
       <c r="K96" s="3">
         <v>28900</v>
       </c>
       <c r="L96" s="3">
+        <v>28900</v>
+      </c>
+      <c r="M96" s="3">
         <v>29000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>29300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>28700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>28900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-29000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-29500</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-29900</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-30300</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-30700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-23900</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X96" s="3">
         <v>-100</v>
       </c>
       <c r="Y96" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-31500</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-100</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-31100</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-31300</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-32100</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-102200</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-30200</v>
       </c>
       <c r="AF96" s="3">
         <v>-30200</v>
       </c>
       <c r="AG96" s="3">
+        <v>-30200</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-30900</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-118900</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-28800</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-28900</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-30500</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-111800</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-27600</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-27800</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-29600</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-104200</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10467,8 +10704,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10589,8 +10829,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10711,130 +10954,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-51100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-25200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>56800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-27100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>11800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-61900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>42600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-25000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-9400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-52600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>29200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-58900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-38900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-64000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>15700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-40300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-24500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-115200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-26200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-303400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-260600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-75100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-33500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>7800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>413900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-62100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>36800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-102500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-30300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-30200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-36000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-119400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-28800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-28900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-48700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-111200</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-27600</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-27500</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-34700</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-104100</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10874,8 +11123,8 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -10955,126 +11204,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-30700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>29800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-11200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-27000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>10700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>20300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-54900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-46200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-18700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-240000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-184300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-28800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>160600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>73700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>290500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>29600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>6300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-130700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>67900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-13000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-59600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>5500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>48600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-40800</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-22700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-2000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>60600</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-25900</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-25700</v>
       </c>
     </row>
